--- a/output/full_scan/batch_seq7_2026-09-08.xlsx
+++ b/output/full_scan/batch_seq7_2026-09-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -580,21 +580,21 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6581</v>
+        <v>6805</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>807.9875381851524</v>
+        <v>815.4597895554925</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>111.5</v>
+        <v>2155</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>68.07509326438485</v>
+        <v>58.62514126968682</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.23251805426497</v>
+        <v>29.39597130604304</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.860275149463761</v>
+        <v>0.1781421499201327</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2114673789266612</v>
+        <v>5.015446352235273</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6510</v>
+        <v>6581</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>787.4235094297297</v>
+        <v>807.9875381851524</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3620</v>
+        <v>111.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>71.03604594108148</v>
+        <v>68.07509326438485</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.07919156006371</v>
+        <v>24.23251805426497</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.842350942972969</v>
+        <v>1.860275149463761</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>96.56998051066324</v>
+        <v>0.2114673789266612</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6530</v>
+        <v>6510</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>771.6127987429013</v>
+        <v>787.4235094297297</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>98.5</v>
+        <v>3620</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>61.52662751617132</v>
+        <v>71.03604594108148</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.15407456986337</v>
+        <v>27.07919156006371</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.661279874290127</v>
+        <v>1.842350942972969</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.191074355742263</v>
+        <v>96.56998051066324</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6739</v>
+        <v>6530</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>716.3647992072173</v>
+        <v>771.6127987429013</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1145</v>
+        <v>98.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.02709437511997</v>
+        <v>61.52662751617132</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13.984057446497</v>
+        <v>24.15407456986337</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.191543053444153</v>
+        <v>1.661279874290127</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>12.92781940845479</v>
+        <v>1.191074355742263</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6655</v>
+        <v>6739</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>703.5431853928742</v>
+        <v>716.3647992072173</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>122.5</v>
+        <v>1145</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>53.01038271638706</v>
+        <v>57.02709437511997</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.32596271330607</v>
+        <v>13.984057446497</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.454318539287424</v>
+        <v>1.191543053444153</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2448701427143018</v>
+        <v>12.92781940845479</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6830</v>
+        <v>6655</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>691.1829931316701</v>
+        <v>703.5431853928742</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>576</v>
+        <v>122.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.97606083647585</v>
+        <v>53.01038271638706</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>35.05848449154948</v>
+        <v>15.32596271330607</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.7454029293515277</v>
+        <v>3.454318539287424</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>9.87545992393934</v>
+        <v>0.2448701427143018</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6588</v>
+        <v>6830</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>684.3694031355686</v>
+        <v>691.1829931316701</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>113.5</v>
+        <v>576</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>59.75365854023934</v>
+        <v>65.97606083647585</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.08306213517497</v>
+        <v>35.05848449154948</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.678637105203226</v>
+        <v>0.7454029293515277</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.3951488727335555</v>
+        <v>9.87545992393934</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6657</v>
+        <v>6588</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>676.4330709280815</v>
+        <v>684.3694031355686</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33.45</v>
+        <v>113.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.42251920751843</v>
+        <v>59.75365854023934</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>19.98045023921188</v>
+        <v>27.08306213517497</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.352782452997447</v>
+        <v>2.678637105203226</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3780484897678425</v>
+        <v>0.3951488727335555</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6670</v>
+        <v>6657</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>672.7388875858564</v>
+        <v>676.4330709280815</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>279</v>
+        <v>33.45</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.14430031136186</v>
+        <v>63.42251920751843</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>29.47392500979507</v>
+        <v>19.98045023921188</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8366948029605334</v>
+        <v>3.352782452997447</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.6678902228822592</v>
+        <v>0.3780484897678425</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6532</v>
+        <v>6670</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>665.9749279451078</v>
+        <v>672.7388875858564</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>279</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.83151097987987</v>
+        <v>58.14430031136186</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>44.48921964937562</v>
+        <v>29.47392500979507</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7045845175640608</v>
+        <v>0.8366948029605334</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5872639688459849</v>
+        <v>0.6678902228822592</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6533</v>
+        <v>6532</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>658.1244777995367</v>
+        <v>665.9749279451078</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>256</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.31645317860194</v>
+        <v>66.83151097987987</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.59510240715208</v>
+        <v>44.48921964937562</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.049797200793246</v>
+        <v>0.7045845175640608</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-1.409431921226897</v>
+        <v>0.5872639688459849</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6505</v>
+        <v>6533</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>652.2272426664366</v>
+        <v>658.1244777995367</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>256</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>61.66986271224469</v>
+        <v>55.31645317860194</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.34129503264692</v>
+        <v>20.59510240715208</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5409916116893145</v>
+        <v>1.049797200793246</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.676320454755194</v>
+        <v>-1.409431921226897</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6782</v>
+        <v>6505</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>649.3645874074633</v>
+        <v>652.2272426664366</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>232.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>57.92359178798345</v>
+        <v>61.66986271224469</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.81349401872309</v>
+        <v>32.34129503264692</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3835938466164204</v>
+        <v>0.5409916116893145</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.5727923050246773</v>
+        <v>0.676320454755194</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6727</v>
+        <v>6782</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>621.854036428472</v>
+        <v>649.3645874074633</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>526</v>
+        <v>232.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.25381482103063</v>
+        <v>57.92359178798345</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30.64827510212573</v>
+        <v>27.81349401872309</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7609436016967338</v>
+        <v>0.3835938466164204</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.170127808636295</v>
+        <v>-0.5727923050246773</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6654</v>
+        <v>6727</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>614.8141167319994</v>
+        <v>621.854036428472</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>222.5</v>
+        <v>526</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.19107648768524</v>
+        <v>59.25381482103063</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>27.32291020442001</v>
+        <v>30.64827510212573</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.207029643885595</v>
+        <v>0.7609436016967338</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>5.597433267207718</v>
+        <v>3.170127808636295</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6829</v>
+        <v>6654</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>609.3894902118892</v>
+        <v>614.8141167319994</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>241</v>
+        <v>222.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.64009987898178</v>
+        <v>70.19107648768524</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>21.35578925369183</v>
+        <v>27.32291020442001</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.9232024474365356</v>
+        <v>2.207029643885595</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.31807677467665</v>
+        <v>5.597433267207718</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6743</v>
+        <v>6829</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>599.1604434648302</v>
+        <v>609.3894902118892</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>29</v>
+        <v>241</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>61.2254178782665</v>
+        <v>55.64009987898178</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.34079740710844</v>
+        <v>21.35578925369183</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.216044346483017</v>
+        <v>0.9232024474365356</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4163227996963316</v>
+        <v>1.31807677467665</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6716</v>
+        <v>6743</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>573.6854023759089</v>
+        <v>599.1604434648302</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.4259111914663</v>
+        <v>61.2254178782665</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>30.05719162648512</v>
+        <v>22.34079740710844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.459437393857398</v>
+        <v>1.216044346483017</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-2.414504541360925</v>
+        <v>0.4163227996963316</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6666</v>
+        <v>6716</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>572.4818588669455</v>
+        <v>573.6854023759089</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>44.95</v>
+        <v>118</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.58012561731074</v>
+        <v>51.4259111914663</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15.22425713246233</v>
+        <v>30.05719162648512</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8183902512783009</v>
+        <v>1.459437393857398</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1081403403086783</v>
+        <v>-2.414504541360925</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6640</v>
+        <v>6666</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>566.9780300626854</v>
+        <v>572.4818588669455</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1215</v>
+        <v>44.95</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.14258787859745</v>
+        <v>59.58012561731074</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>28.65820612065306</v>
+        <v>15.22425713246233</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.247341789968514</v>
+        <v>0.8183902512783009</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>23.55205818773954</v>
+        <v>0.1081403403086783</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6667</v>
+        <v>6640</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>552.925971978506</v>
+        <v>566.9780300626854</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>250</v>
+        <v>1215</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.20509977396731</v>
+        <v>60.14258787859745</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.0461331850586</v>
+        <v>28.65820612065306</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.330480518231412</v>
+        <v>1.247341789968514</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>4.527299269435721</v>
+        <v>23.55205818773954</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6693</v>
+        <v>6667</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>545.9061901017802</v>
+        <v>552.925971978506</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>187.5</v>
+        <v>250</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.21787439403974</v>
+        <v>65.20509977396731</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.41705678290198</v>
+        <v>31.0461331850586</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.360524250159607</v>
+        <v>2.330480518231412</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.493424396923188</v>
+        <v>4.527299269435721</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6770</v>
+        <v>6693</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>545.0736672183192</v>
+        <v>545.9061901017802</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>187.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.27616693690177</v>
+        <v>56.21787439403974</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10.9712794406098</v>
+        <v>16.41705678290198</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8444261888537185</v>
+        <v>1.360524250159607</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1051504909543317</v>
+        <v>2.493424396923188</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6668</v>
+        <v>6770</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>533.2850616149232</v>
+        <v>545.0736672183192</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>40.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.24058221374786</v>
+        <v>55.27616693690177</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>34.31814427725422</v>
+        <v>10.9712794406098</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.350992756699952</v>
+        <v>0.8444261888537185</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1392490265551558</v>
+        <v>0.1051504909543317</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6643</v>
+        <v>6668</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>533.0093059432996</v>
+        <v>533.2850616149232</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>438</v>
+        <v>40.2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,119 +1877,119 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.39062250063194</v>
+        <v>53.24058221374786</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.97129845860491</v>
+        <v>34.31814427725422</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.814101315049006</v>
+        <v>0.350992756699952</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.118519231517886</v>
+        <v>0.1392490265551558</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6806</v>
+        <v>6643</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>533.0093059432996</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>3.51</v>
+        <v>438</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G28" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>31.69502333421417</v>
+        <v>54.39062250063194</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.59323721587091</v>
+        <v>10.97129845860491</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>2.814101315049006</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.4112822135265479</v>
+        <v>1.118519231517886</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6672</v>
+        <v>6806</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>526.8822395587974</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>294</v>
+        <v>3.51</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>59.6422552771047</v>
+        <v>31.69502333421417</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>18.54230369276637</v>
+        <v>32.59323721587091</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.418154031011875</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.043001680577321</v>
+        <v>0.4112822135265479</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6834</v>
+        <v>6672</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>524.4865771090791</v>
+        <v>526.8822395587974</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>98.7</v>
+        <v>294</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>55.05408800314154</v>
+        <v>59.6422552771047</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11.14741260787161</v>
+        <v>18.54230369276637</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.939674338127303</v>
+        <v>1.418154031011875</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7314845448288374</v>
+        <v>1.043001680577321</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6491</v>
+        <v>6834</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>519.8261360697823</v>
+        <v>524.4865771090791</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>376</v>
+        <v>98.7</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>51.75342635659707</v>
+        <v>55.05408800314154</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.72364245054425</v>
+        <v>11.14741260787161</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3197010122355047</v>
+        <v>1.939674338127303</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.221934914605328</v>
+        <v>0.7314845448288374</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6669</v>
+        <v>6491</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>518.6708320038472</v>
+        <v>519.8261360697823</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2340</v>
+        <v>376</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>25.93917649178687</v>
+        <v>51.75342635659707</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>37.3528254221992</v>
+        <v>27.72364245054425</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.767083200384725</v>
+        <v>0.3197010122355047</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-554.1182177600169</v>
+        <v>-1.221934914605328</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6753</v>
+        <v>6669</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>515.7572046040624</v>
+        <v>518.6708320038472</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>134.5</v>
+        <v>2340</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43.26018227523498</v>
+        <v>25.93917649178687</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.4120776048576</v>
+        <v>37.3528254221992</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3616246030484726</v>
+        <v>1.767083200384725</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.9600352608017964</v>
+        <v>-554.1182177600169</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6651</v>
+        <v>6753</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>505.9746981862054</v>
+        <v>515.7572046040624</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>142.5</v>
+        <v>134.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>50.19720953684873</v>
+        <v>43.26018227523498</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.75305895666948</v>
+        <v>21.4120776048576</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9703064140740332</v>
+        <v>0.3616246030484726</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.3456165906705823</v>
+        <v>-0.9600352608017964</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6598</v>
+        <v>6651</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>433.6321897192381</v>
+        <v>505.9746981862054</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>28.4</v>
+        <v>142.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.15959838765468</v>
+        <v>50.19720953684873</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.57406752938354</v>
+        <v>27.75305895666948</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.261431628619163</v>
+        <v>0.9703064140740332</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1376147834908983</v>
+        <v>-0.3456165906705823</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6789</v>
+        <v>6598</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>431.6941864163743</v>
+        <v>433.6321897192381</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>463</v>
+        <v>28.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.73734103811157</v>
+        <v>53.15959838765468</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>16.2333400389604</v>
+        <v>17.57406752938354</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7609440861540149</v>
+        <v>1.261431628619163</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3.977906864518607</v>
+        <v>-0.1376147834908983</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6664</v>
+        <v>6789</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>430.1254708315474</v>
+        <v>431.6941864163743</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>356.5</v>
+        <v>463</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.88775435429002</v>
+        <v>51.73734103811157</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13.23794773443468</v>
+        <v>16.2333400389604</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4631079346494791</v>
+        <v>0.7609440861540149</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.439799242354692</v>
+        <v>3.977906864518607</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6741</v>
+        <v>6664</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>423.5194451879296</v>
+        <v>430.1254708315474</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>59.4</v>
+        <v>356.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>57.4608773682677</v>
+        <v>50.88775435429002</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.63072036462111</v>
+        <v>13.23794773443468</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4887712184020217</v>
+        <v>0.4631079346494791</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3050556153030777</v>
+        <v>1.439799242354692</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6606</v>
+        <v>6741</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>420.6331678956973</v>
+        <v>423.5194451879296</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>25.85</v>
+        <v>59.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.60926839498769</v>
+        <v>57.4608773682677</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.54836097661536</v>
+        <v>30.63072036462111</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.165786866872735</v>
+        <v>0.4887712184020217</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0839090479213182</v>
+        <v>0.3050556153030777</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6771</v>
+        <v>6606</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>416.0392425413676</v>
+        <v>420.6331678956973</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>41.8</v>
+        <v>25.85</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.22295237410648</v>
+        <v>49.60926839498769</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.87902779538661</v>
+        <v>11.54836097661536</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3022235505962923</v>
+        <v>1.165786866872735</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1143612713677854</v>
+        <v>-0.0839090479213182</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6792</v>
+        <v>6771</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>401.2813522093994</v>
+        <v>416.0392425413676</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>60.2</v>
+        <v>41.8</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.53748224410143</v>
+        <v>57.22295237410648</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.46728964532433</v>
+        <v>29.87902779538661</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>4.772379194158602</v>
+        <v>0.3022235505962923</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1306550689305336</v>
+        <v>-0.1143612713677854</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6526</v>
+        <v>6792</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>398.3064981384258</v>
+        <v>401.2813522093994</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>643</v>
+        <v>60.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>57.32468647783924</v>
+        <v>57.53748224410143</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.3395374108772</v>
+        <v>16.46728964532433</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6587456627398385</v>
+        <v>4.772379194158602</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>5.436709734456363</v>
+        <v>0.1306550689305336</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6613</v>
+        <v>6526</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>392.2011083188405</v>
+        <v>398.3064981384258</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>258.5</v>
+        <v>643</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.26715616788743</v>
+        <v>57.32468647783924</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.06474676510794</v>
+        <v>17.3395374108772</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4304437994719747</v>
+        <v>0.6587456627398385</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.873509740039921</v>
+        <v>5.436709734456363</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6584</v>
+        <v>6613</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>387.4361986958692</v>
+        <v>392.2011083188405</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>602</v>
+        <v>258.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.87300448435168</v>
+        <v>43.26715616788743</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>23.99370474683624</v>
+        <v>10.06474676510794</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3555360189236659</v>
+        <v>0.4304437994719747</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.366555125694628</v>
+        <v>1.873509740039921</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6517</v>
+        <v>6584</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>382.2339520605183</v>
+        <v>387.4361986958692</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>65.5</v>
+        <v>602</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.5019483359877</v>
+        <v>49.87300448435168</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>17.00599894183177</v>
+        <v>23.99370474683624</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4538543088114936</v>
+        <v>0.3555360189236659</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.1752640585001097</v>
+        <v>-0.366555125694628</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6720</v>
+        <v>6517</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>379.402329000225</v>
+        <v>382.2339520605183</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>131.5</v>
+        <v>65.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>41.89355101177274</v>
+        <v>46.5019483359877</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>29.7809957832199</v>
+        <v>17.00599894183177</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.635973977107271</v>
+        <v>0.4538543088114936</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.209990861034385</v>
+        <v>-0.1752640585001097</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6512</v>
+        <v>6720</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>363.8408931041609</v>
+        <v>379.402329000225</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>20.85</v>
+        <v>131.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.98486382158959</v>
+        <v>41.89355101177274</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>9.357136556777196</v>
+        <v>29.7809957832199</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.406853712179754</v>
+        <v>1.635973977107271</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.576528712478221</v>
+        <v>-0.209990861034385</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6715</v>
+        <v>6512</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>359.8740304803192</v>
+        <v>363.8408931041609</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>325</v>
+        <v>20.85</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>42.64360276564915</v>
+        <v>52.98486382158959</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12.96959218413193</v>
+        <v>9.357136556777196</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.5349186262015357</v>
+        <v>1.406853712179754</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-5.67429992655587</v>
+        <v>0.576528712478221</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6477</v>
+        <v>6715</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>359.2219998495567</v>
+        <v>359.8740304803192</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>34.2</v>
+        <v>325</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>41.7583777042333</v>
+        <v>42.64360276564915</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.15213841255892</v>
+        <v>12.96959218413193</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2027386582900327</v>
+        <v>0.5349186262015357</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.2970818146771114</v>
+        <v>-5.67429992655587</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6674</v>
+        <v>6477</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>358.8157255218155</v>
+        <v>359.2219998495567</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>16.15</v>
+        <v>34.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.89098457090631</v>
+        <v>41.7583777042333</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.63986735436038</v>
+        <v>16.15213841255892</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3483767593897826</v>
+        <v>0.2027386582900327</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0684501952890897</v>
+        <v>-0.2970818146771114</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6568</v>
+        <v>6674</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>358.5675713208705</v>
+        <v>358.8157255218155</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>134.5</v>
+        <v>16.15</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.84694401270173</v>
+        <v>53.89098457090631</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>29.4789115856213</v>
+        <v>23.63986735436038</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7218356628444</v>
+        <v>0.3483767593897826</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.529900967195629</v>
+        <v>0.0684501952890897</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3177,21 +3177,21 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6486</v>
+        <v>6568</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>349.4467450518248</v>
+        <v>358.5675713208705</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>134.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>65.02749482188355</v>
+        <v>48.84694401270173</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>37.08606379728727</v>
+        <v>29.4789115856213</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7446745051824833</v>
+        <v>0.7218356628444</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.944239237720334</v>
+        <v>1.529900967195629</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6658</v>
+        <v>6486</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>349.2044488267212</v>
+        <v>349.4467450518248</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>171.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.11224208903591</v>
+        <v>65.02749482188355</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.67328011474936</v>
+        <v>37.08606379728727</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6106628637618509</v>
+        <v>0.7446745051824833</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.385528761281418</v>
+        <v>0.944239237720334</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6642</v>
+        <v>6658</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>336.9827089431796</v>
+        <v>349.2044488267212</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>76.8</v>
+        <v>171.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.25129108117788</v>
+        <v>52.11224208903591</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.21349579573762</v>
+        <v>17.67328011474936</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.9358861256626564</v>
+        <v>0.6106628637618509</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.2222394848502142</v>
+        <v>1.385528761281418</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6691</v>
+        <v>6642</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>335.9191470384818</v>
+        <v>336.9827089431796</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>615</v>
+        <v>76.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>40.50007415269391</v>
+        <v>44.25129108117788</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.07976892898897</v>
+        <v>18.21349579573762</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3705050608640028</v>
+        <v>0.9358861256626564</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.3831669952697112</v>
+        <v>-0.2222394848502142</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6788</v>
+        <v>6691</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>335.8143137725976</v>
+        <v>335.9191470384818</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>348</v>
+        <v>615</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>44.37709759653392</v>
+        <v>40.50007415269391</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15.45190241098726</v>
+        <v>22.07976892898897</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8306806619963882</v>
+        <v>0.3705050608640028</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.046603330817496</v>
+        <v>-0.3831669952697112</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6722</v>
+        <v>6788</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>334.7500928306542</v>
+        <v>335.8143137725976</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>32.55</v>
+        <v>348</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>42.39458154427081</v>
+        <v>44.37709759653392</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.60879481780431</v>
+        <v>15.45190241098726</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.701540343478891</v>
+        <v>0.8306806619963882</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0899954914945619</v>
+        <v>-0.046603330817496</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6761</v>
+        <v>6722</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>328.0546696554105</v>
+        <v>334.7500928306542</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>175</v>
+        <v>32.55</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.55257196389697</v>
+        <v>42.39458154427081</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.71597688110672</v>
+        <v>23.60879481780431</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4342300012605422</v>
+        <v>1.701540343478891</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.238670077344167</v>
+        <v>0.0899954914945619</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6823</v>
+        <v>6761</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>322.810171766636</v>
+        <v>328.0546696554105</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>60</v>
+        <v>175</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.54211804711826</v>
+        <v>46.55257196389697</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.2814931295494</v>
+        <v>18.71597688110672</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4294533416838149</v>
+        <v>0.4342300012605422</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.112943744197653</v>
+        <v>-1.238670077344167</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6754</v>
+        <v>6823</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>320.481901673203</v>
+        <v>322.810171766636</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>42.75</v>
+        <v>60</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>56.29708777801369</v>
+        <v>38.54211804711826</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12.42973679499116</v>
+        <v>21.2814931295494</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.331748338992626</v>
+        <v>0.4294533416838149</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1121784270907718</v>
+        <v>-0.112943744197653</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6811</v>
+        <v>6754</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>319.3804075938347</v>
+        <v>320.481901673203</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>224</v>
+        <v>42.75</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.78859764787369</v>
+        <v>56.29708777801369</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>10.79510120197438</v>
+        <v>12.42973679499116</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7187324688276999</v>
+        <v>1.331748338992626</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.4063333712460554</v>
+        <v>0.1121784270907718</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6680</v>
+        <v>6811</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>313.9164022312246</v>
+        <v>319.3804075938347</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>52.2</v>
+        <v>224</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.20339788153497</v>
+        <v>47.78859764787369</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7.569005757480713</v>
+        <v>10.79510120197438</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.617097772895236</v>
+        <v>0.7187324688276999</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>2.098562896681043</v>
+        <v>-0.4063333712460554</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6768</v>
+        <v>6680</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>313.865084682437</v>
+        <v>313.9164022312246</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>63.7</v>
+        <v>52.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>35.15412713719567</v>
+        <v>52.20339788153497</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.09054584343714</v>
+        <v>7.569005757480713</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2737022867166535</v>
+        <v>1.617097772895236</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.19075380579163</v>
+        <v>2.098562896681043</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6756</v>
+        <v>6768</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>312.8409634872693</v>
+        <v>313.865084682437</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.3</v>
+        <v>63.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.91247846497375</v>
+        <v>35.15412713719567</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11.50661678457034</v>
+        <v>28.09054584343714</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.419828576370608</v>
+        <v>0.2737022867166535</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1840528792783768</v>
+        <v>0.19075380579163</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6548</v>
+        <v>6756</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>310.1838950406027</v>
+        <v>312.8409634872693</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.86784484278812</v>
+        <v>47.91247846497375</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.09194777242854</v>
+        <v>11.50661678457034</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.149242981737483</v>
+        <v>1.419828576370608</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1220629855635588</v>
+        <v>-0.1840528792783768</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6525</v>
+        <v>6548</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>295.9339720519251</v>
+        <v>310.1838950406027</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>130.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>40.67466187954505</v>
+        <v>45.86784484278812</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.385231231066143</v>
+        <v>12.09194777242854</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5615100192852857</v>
+        <v>1.149242981737483</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.6107451992790849</v>
+        <v>0.1220629855635588</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6807</v>
+        <v>6525</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>293.2939939629893</v>
+        <v>295.9339720519251</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>33.35</v>
+        <v>130.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>39.76908227305419</v>
+        <v>40.67466187954505</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.75036276885498</v>
+        <v>9.385231231066143</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.1377883326671212</v>
+        <v>0.5615100192852857</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.2825429186194249</v>
+        <v>-0.6107451992790849</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6645</v>
+        <v>6807</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>287.7963854067276</v>
+        <v>293.2939939629893</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>12.2</v>
+        <v>33.35</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>33.99019362872913</v>
+        <v>39.76908227305419</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>30.43245177141639</v>
+        <v>23.75036276885498</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.144977701439053</v>
+        <v>0.1377883326671212</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0212332110595538</v>
+        <v>-0.2825429186194249</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6561</v>
+        <v>6645</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>287.0054770241093</v>
+        <v>287.7963854067276</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>320</v>
+        <v>12.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>43.9083169135635</v>
+        <v>33.99019362872913</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.652648581715585</v>
+        <v>30.43245177141639</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8996719727072888</v>
+        <v>2.144977701439053</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.2160678663758344</v>
+        <v>-0.0212332110595538</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6494</v>
+        <v>6561</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>285.9201530544566</v>
+        <v>287.0054770241093</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>53.6</v>
+        <v>320</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.25311551016454</v>
+        <v>43.9083169135635</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>9.961776431188325</v>
+        <v>7.652648581715585</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7385445798837316</v>
+        <v>0.8996719727072888</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0647145395700766</v>
+        <v>0.2160678663758344</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6725</v>
+        <v>6494</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>282.2383640201637</v>
+        <v>285.9201530544566</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>223</v>
+        <v>53.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>39.59431832594806</v>
+        <v>46.25311551016454</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>30.40761259730545</v>
+        <v>9.961776431188325</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7933761603754114</v>
+        <v>0.7385445798837316</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>2.112668727597777</v>
+        <v>0.0647145395700766</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6531</v>
+        <v>6725</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>276.4070315475272</v>
+        <v>282.2383640201637</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>931</v>
+        <v>223</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>53.85169553207633</v>
+        <v>39.59431832594806</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.12126184913654</v>
+        <v>30.40761259730545</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7112762250632148</v>
+        <v>0.7933761603754114</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>4.601079891702231</v>
+        <v>2.112668727597777</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6831</v>
+        <v>6531</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>272.6900444004926</v>
+        <v>276.4070315475272</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>560</v>
+        <v>931</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>41.3615659212771</v>
+        <v>53.85169553207633</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.19993559145919</v>
+        <v>11.12126184913654</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6621006966827996</v>
+        <v>0.7112762250632148</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.7930900526689406</v>
+        <v>4.601079891702231</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4343,21 +4343,21 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6534</v>
+        <v>6831</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>272.4461039044302</v>
+        <v>272.6900444004926</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>560</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.79703784899225</v>
+        <v>41.3615659212771</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12.78449770086773</v>
+        <v>13.19993559145919</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5279845051673413</v>
+        <v>0.6621006966827996</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0065504682473384</v>
+        <v>-0.7930900526689406</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6579</v>
+        <v>6534</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>272.3614076043211</v>
+        <v>272.4461039044302</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>147.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.56858913287873</v>
+        <v>48.79703784899225</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.95800536489087</v>
+        <v>12.78449770086773</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9396776424277888</v>
+        <v>0.5279845051673413</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.469766649499451</v>
+        <v>-0.0065504682473384</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6692</v>
+        <v>6579</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>268.3090885944459</v>
+        <v>272.3614076043211</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>23.65</v>
+        <v>147.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.24070551908524</v>
+        <v>44.56858913287873</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.568418580120449</v>
+        <v>16.95800536489087</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.284198941387142</v>
+        <v>0.9396776424277888</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0832257924894131</v>
+        <v>0.469766649499451</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6504</v>
+        <v>6692</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>266.8408252657883</v>
+        <v>268.3090885944459</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>37.35</v>
+        <v>23.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.72147040342129</v>
+        <v>50.24070551908524</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.15092922851503</v>
+        <v>8.568418580120449</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.041631721383055</v>
+        <v>1.284198941387142</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.070421212934255</v>
+        <v>-0.0832257924894131</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6679</v>
+        <v>6504</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>266.6383154747843</v>
+        <v>266.8408252657883</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>199.5</v>
+        <v>37.35</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.57590029691466</v>
+        <v>45.72147040342129</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.76558262600653</v>
+        <v>12.15092922851503</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.416883653677798</v>
+        <v>1.041631721383055</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>1.625335034354517</v>
+        <v>-0.070421212934255</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6573</v>
+        <v>6679</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>265.621369350562</v>
+        <v>266.6383154747843</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>16.3</v>
+        <v>199.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>43.08162536400654</v>
+        <v>41.57590029691466</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.95059425263248</v>
+        <v>16.76558262600653</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5679351437558144</v>
+        <v>2.416883653677798</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0388581505549998</v>
+        <v>1.625335034354517</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6570</v>
+        <v>6573</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>263.7297345483679</v>
+        <v>265.621369350562</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>48.45</v>
+        <v>16.3</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>35.41632963849233</v>
+        <v>43.08162536400654</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.70143945470885</v>
+        <v>18.95059425263248</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.859817412280172</v>
+        <v>0.5679351437558144</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.51647683611254</v>
+        <v>-0.0388581505549998</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6706</v>
+        <v>6570</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>262.8581684312927</v>
+        <v>263.7297345483679</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>123</v>
+        <v>48.45</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.54827079826302</v>
+        <v>35.41632963849233</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.80249729675971</v>
+        <v>17.70143945470885</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4740773091169278</v>
+        <v>1.859817412280172</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.7058882252734793</v>
+        <v>-0.51647683611254</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6735</v>
+        <v>6706</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>261.9489614280106</v>
+        <v>262.8581684312927</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>62.1</v>
+        <v>123</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.0810034263398</v>
+        <v>51.54827079826302</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14.18131651855943</v>
+        <v>17.80249729675971</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6481080302192266</v>
+        <v>0.4740773091169278</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.4057059345836085</v>
+        <v>0.7058882252734793</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6719</v>
+        <v>6735</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>259.2524099272269</v>
+        <v>261.9489614280106</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>183.5</v>
+        <v>62.1</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>35.11227800982896</v>
+        <v>43.0810034263398</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.09587822925583</v>
+        <v>14.18131651855943</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.185153466312751</v>
+        <v>0.6481080302192266</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.7479382868846702</v>
+        <v>0.4057059345836085</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6541</v>
+        <v>6719</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>256.160755583048</v>
+        <v>259.2524099272269</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>31.8</v>
+        <v>183.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>29.23235169232726</v>
+        <v>35.11227800982896</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>25.77542272718778</v>
+        <v>23.09587822925583</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5356450728194783</v>
+        <v>1.185153466312751</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.4002104727545834</v>
+        <v>0.7479382868846702</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6742</v>
+        <v>6541</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>252.4005034803284</v>
+        <v>256.160755583048</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44.25</v>
+        <v>31.8</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.87998733082897</v>
+        <v>29.23235169232726</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20.76496896418658</v>
+        <v>25.77542272718778</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.105939905194558</v>
+        <v>0.5356450728194783</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3414988231650095</v>
+        <v>-0.4002104727545834</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6695</v>
+        <v>6742</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>246.9102171076397</v>
+        <v>252.4005034803284</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>47.1</v>
+        <v>44.25</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.40995849604863</v>
+        <v>46.87998733082897</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.3497134195223</v>
+        <v>20.76496896418658</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.194659025747187</v>
+        <v>1.105939905194558</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.149430021073333</v>
+        <v>0.3414988231650095</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6796</v>
+        <v>6695</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>246.9025456112034</v>
+        <v>246.9102171076397</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>56.8</v>
+        <v>47.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.61727319279354</v>
+        <v>41.40995849604863</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>23.75860771213402</v>
+        <v>12.3497134195223</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.09025456112034</v>
+        <v>1.194659025747187</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.5449434521108285</v>
+        <v>0.149430021073333</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6684</v>
+        <v>6796</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>242.7317449580232</v>
+        <v>246.9025456112034</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>45.4</v>
+        <v>56.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.37773885417946</v>
+        <v>38.61727319279354</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.47122149410082</v>
+        <v>23.75860771213402</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.104967120705972</v>
+        <v>1.09025456112034</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0243899799165132</v>
+        <v>-0.5449434521108285</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6582</v>
+        <v>6684</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>234.852677194024</v>
+        <v>242.7317449580232</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>31.95</v>
+        <v>45.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>47.86395129638774</v>
+        <v>40.37773885417946</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>24.75978711096207</v>
+        <v>10.47122149410082</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3660841901424685</v>
+        <v>1.104967120705972</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0426054252348181</v>
+        <v>0.0243899799165132</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6698</v>
+        <v>6582</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>233.513821378584</v>
+        <v>234.852677194024</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>31.5</v>
+        <v>31.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.34479728180693</v>
+        <v>47.86395129638774</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.06867524183938</v>
+        <v>24.75978711096207</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6961914702436042</v>
+        <v>0.3660841901424685</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1566858955208776</v>
+        <v>-0.0426054252348181</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6589</v>
+        <v>6698</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>232.083092737028</v>
+        <v>233.513821378584</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>47.45</v>
+        <v>31.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.70034525857132</v>
+        <v>43.34479728180693</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.1242434305547</v>
+        <v>17.06867524183938</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8558878811768484</v>
+        <v>0.6961914702436042</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.4012069413680502</v>
+        <v>0.1566858955208776</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6689</v>
+        <v>6589</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>231.6292404839744</v>
+        <v>232.083092737028</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>61</v>
+        <v>47.45</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.09932361759533</v>
+        <v>43.70034525857132</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.68230718578359</v>
+        <v>18.1242434305547</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4917632550444172</v>
+        <v>0.8558878811768484</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0140046565404236</v>
+        <v>-0.4012069413680502</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6597</v>
+        <v>6689</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>230.4827225183541</v>
+        <v>231.6292404839744</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.82741484759838</v>
+        <v>47.09932361759533</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7.742518479759546</v>
+        <v>11.68230718578359</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0</v>
+        <v>0.4917632550444172</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.745134151039839</v>
+        <v>-0.0140046565404236</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6585</v>
+        <v>6597</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>229.6143011600642</v>
+        <v>230.4827225183541</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.50841738230459</v>
+        <v>43.82741484759838</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.70417306817032</v>
+        <v>7.742518479759546</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7797764111011348</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0612101809423408</v>
+        <v>-1.745134151039839</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6488</v>
+        <v>6585</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>226.7521580514465</v>
+        <v>229.6143011600642</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>955</v>
+        <v>111</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.03012043068672</v>
+        <v>41.50841738230459</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>8.055558888587148</v>
+        <v>18.70417306817032</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.922176871053513</v>
+        <v>0.7797764111011348</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>3.48371426682341</v>
+        <v>-0.0612101809423408</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6577</v>
+        <v>6488</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>224.7334897171009</v>
+        <v>226.7521580514465</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>80.3</v>
+        <v>955</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>50.43055413083584</v>
+        <v>48.03012043068672</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.01251245704972</v>
+        <v>8.055558888587148</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7190998798435287</v>
+        <v>0.922176871053513</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.09224063910608921</v>
+        <v>3.48371426682341</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6794</v>
+        <v>6577</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>223.2730627168156</v>
+        <v>224.7334897171009</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>75</v>
+        <v>80.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.20790253543825</v>
+        <v>50.43055413083584</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.99268217282915</v>
+        <v>17.01251245704972</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2272485929701603</v>
+        <v>0.7190998798435287</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1384869086515364</v>
+        <v>-0.09224063910608921</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6683</v>
+        <v>6794</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>218.8228426412554</v>
+        <v>223.2730627168156</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1405</v>
+        <v>75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>57.90194777138226</v>
+        <v>49.20790253543825</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>16.11740772533406</v>
+        <v>17.99268217282915</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.155705169633501</v>
+        <v>0.2272485929701603</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>31.80027082661669</v>
+        <v>0.1384869086515364</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6690</v>
+        <v>6683</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>214.9934743722048</v>
+        <v>218.8228426412554</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>162</v>
+        <v>1405</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.76612122727808</v>
+        <v>57.90194777138226</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.445116997643643</v>
+        <v>16.11740772533406</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4173633786077562</v>
+        <v>1.155705169633501</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1800066459887145</v>
+        <v>31.80027082661669</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6781</v>
+        <v>6690</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>214.9836530993526</v>
+        <v>214.9934743722048</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1065</v>
+        <v>162</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.5818172897796</v>
+        <v>43.76612122727808</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.23558998975148</v>
+        <v>8.445116997643643</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5395635281529145</v>
+        <v>0.4173633786077562</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-3.302532005257573</v>
+        <v>-0.1800066459887145</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6558</v>
+        <v>6781</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>214.1695708601754</v>
+        <v>214.9836530993526</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>23.55</v>
+        <v>1065</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>34.69471362171547</v>
+        <v>47.5818172897796</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>27.3089032411732</v>
+        <v>11.23558998975148</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.336389104380602</v>
+        <v>0.5395635281529145</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0316800725415931</v>
+        <v>-3.302532005257573</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6803</v>
+        <v>6558</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>209.6308928341929</v>
+        <v>214.1695708601754</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>271</v>
+        <v>23.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.67833795774183</v>
+        <v>34.69471362171547</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.52048209643205</v>
+        <v>27.3089032411732</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9949801501279404</v>
+        <v>1.336389104380602</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.4382697898419467</v>
+        <v>-0.0316800725415931</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6498</v>
+        <v>6803</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>208.4327063722208</v>
+        <v>209.6308928341929</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>271</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.11312999632172</v>
+        <v>50.67833795774183</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.24113664487609</v>
+        <v>15.52048209643205</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.003804550992552</v>
+        <v>0.9949801501279404</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.021045931928989</v>
+        <v>0.4382697898419467</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6835</v>
+        <v>6498</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>205.7016424561318</v>
+        <v>208.4327063722208</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>31.15</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.18767441591488</v>
+        <v>40.11312999632172</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.34594228184596</v>
+        <v>19.24113664487609</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.014264432520797</v>
+        <v>2.003804550992552</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1129956182313954</v>
+        <v>0.021045931928989</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6821</v>
+        <v>6835</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>203.7312463603028</v>
+        <v>205.7016424561318</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>40.65</v>
+        <v>31.15</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.62241459278199</v>
+        <v>47.18767441591488</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15.16213075025129</v>
+        <v>13.34594228184596</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.01562198174353</v>
+        <v>2.014264432520797</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2240166460950454</v>
+        <v>0.1129956182313954</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6763</v>
+        <v>6821</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>203.2174630596548</v>
+        <v>203.7312463603028</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>41</v>
+        <v>40.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.39044608417888</v>
+        <v>41.62241459278199</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.6477293317016</v>
+        <v>15.16213075025129</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9734081955473288</v>
+        <v>1.01562198174353</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0248918268214621</v>
+        <v>0.2240166460950454</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6592</v>
+        <v>6763</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>200.1051630496571</v>
+        <v>203.2174630596548</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>60.3</v>
+        <v>41</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.98999106854895</v>
+        <v>39.39044608417888</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>9.15727410960532</v>
+        <v>22.6477293317016</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7123422097328159</v>
+        <v>0.9734081955473288</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0517579352328769</v>
+        <v>-0.0248918268214621</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6757</v>
+        <v>6592</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>199.5876965667088</v>
+        <v>200.1051630496571</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>55.4</v>
+        <v>60.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.10843746805492</v>
+        <v>44.98999106854895</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>9.317084707848922</v>
+        <v>9.15727410960532</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.2965802314484951</v>
+        <v>0.7123422097328159</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0111109495483293</v>
+        <v>-0.0517579352328769</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6560</v>
+        <v>6757</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>191.3584679559912</v>
+        <v>199.5876965667088</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>30.5</v>
+        <v>55.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.56146398449882</v>
+        <v>46.10843746805492</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.37419979458706</v>
+        <v>9.317084707848922</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.278077268643306</v>
+        <v>0.2965802314484951</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.4930554047158586</v>
+        <v>0.0111109495483293</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6790</v>
+        <v>6560</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>187.3827351864433</v>
+        <v>191.3584679559912</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.33078324614023</v>
+        <v>49.56146398449882</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.17506367826329</v>
+        <v>13.37419979458706</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4505233739449951</v>
+        <v>1.278077268643306</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0432821308290801</v>
+        <v>0.4930554047158586</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6605</v>
+        <v>6790</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>178.0019178085848</v>
+        <v>187.3827351864433</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>135.5</v>
+        <v>38</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.84288706203793</v>
+        <v>43.33078324614023</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.55153516700027</v>
+        <v>10.17506367826329</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6276480044032156</v>
+        <v>0.4505233739449951</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.5387575338998242</v>
+        <v>0.0432821308290801</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6591</v>
+        <v>6605</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>177.6955930205658</v>
+        <v>178.0019178085848</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>42.1</v>
+        <v>135.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>35.54307835916889</v>
+        <v>44.84288706203793</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>29.14956357047086</v>
+        <v>12.55153516700027</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3798053636175418</v>
+        <v>0.6276480044032156</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0977069689478654</v>
+        <v>-0.5387575338998242</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6485</v>
+        <v>6591</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>170.9802047688125</v>
+        <v>177.6955930205658</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>60.4</v>
+        <v>42.1</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.07866427439396</v>
+        <v>35.54307835916889</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.65543369723994</v>
+        <v>29.14956357047086</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5343653286018868</v>
+        <v>0.3798053636175418</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.3922438353786046</v>
+        <v>0.0977069689478654</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6556</v>
+        <v>6485</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>165.5786434320172</v>
+        <v>170.9802047688125</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>61.4</v>
+        <v>60.4</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>47.1157731209621</v>
+        <v>44.07866427439396</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.25650284673332</v>
+        <v>15.65543369723994</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1546236331915091</v>
+        <v>0.5343653286018868</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.4098829632022718</v>
+        <v>0.3922438353786046</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6641</v>
+        <v>6556</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>164.8408619343973</v>
+        <v>165.5786434320172</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.1</v>
+        <v>61.4</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>35.86094615136281</v>
+        <v>47.1157731209621</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.149508765375364</v>
+        <v>13.25650284673332</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.8067832214715107</v>
+        <v>0.1546236331915091</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.07192504325461541</v>
+        <v>0.4098829632022718</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6708</v>
+        <v>6641</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>164.6651133567202</v>
+        <v>164.8408619343973</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>38</v>
+        <v>17.1</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.38260303425558</v>
+        <v>35.86094615136281</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>6.883095893920267</v>
+        <v>8.149508765375364</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3665113356720247</v>
+        <v>0.8067832214715107</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.07450330760204039</v>
+        <v>-0.07192504325461541</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6799</v>
+        <v>6708</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>156.9441067001134</v>
+        <v>164.6651133567202</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>78.3</v>
+        <v>38</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.6353371647083</v>
+        <v>51.38260303425558</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.8604495400668</v>
+        <v>6.883095893920267</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.7879506114084703</v>
+        <v>0.3665113356720247</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1211228477043699</v>
+        <v>-0.07450330760204039</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6625</v>
+        <v>6799</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>156.254382090671</v>
+        <v>156.9441067001134</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.39035510466313</v>
+        <v>40.6353371647083</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8.982284798071634</v>
+        <v>11.8604495400668</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.8792739144100871</v>
+        <v>0.7879506114084703</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.168948397900651</v>
+        <v>0.1211228477043699</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6732</v>
+        <v>6625</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>140.8139561339498</v>
+        <v>156.254382090671</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>146.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>35.69159476467141</v>
+        <v>45.39035510466313</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.67999266327133</v>
+        <v>8.982284798071634</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.957959552056716</v>
+        <v>0.8792739144100871</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.325071442008789</v>
+        <v>-0.168948397900651</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6776</v>
+        <v>6732</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>137.6844716726152</v>
+        <v>140.8139561339498</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>52.4</v>
+        <v>146.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>37.24286997663048</v>
+        <v>35.69159476467141</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.03571225418198</v>
+        <v>18.67999266327133</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.044958644411857</v>
+        <v>0.957959552056716</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0140246522484243</v>
+        <v>0.325071442008789</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6624</v>
+        <v>6776</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>134.9094670578778</v>
+        <v>137.6844716726152</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0</v>
+        <v>52.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>37.19851091248522</v>
+        <v>37.24286997663048</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>9.416048773021378</v>
+        <v>16.03571225418198</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0</v>
+        <v>1.044958644411857</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-3.964665944279522</v>
+        <v>-0.0140246522484243</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6614</v>
+        <v>6624</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>127.0170896681341</v>
+        <v>134.9094670578778</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>35.85</v>
+        <v>0</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.08696083652589</v>
+        <v>37.19851091248522</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.523980856852001</v>
+        <v>9.416048773021378</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5927063975764559</v>
+        <v>0</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0970641028038076</v>
+        <v>-3.964665944279522</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6671</v>
+        <v>6614</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>125.6316700689974</v>
+        <v>127.0170896681341</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>23.1</v>
+        <v>35.85</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>49.41068145384219</v>
+        <v>44.08696083652589</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.72757638369508</v>
+        <v>9.523980856852001</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5299810986132798</v>
+        <v>0.5927063975764559</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.06889577087031271</v>
+        <v>0.0970641028038076</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6546</v>
+        <v>6671</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>122.9643128989748</v>
+        <v>125.6316700689974</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>60.8</v>
+        <v>23.1</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.31637812868967</v>
+        <v>49.41068145384219</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.83901659727469</v>
+        <v>14.72757638369508</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5149844874899007</v>
+        <v>0.5299810986132798</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1271427532583298</v>
+        <v>0.06889577087031271</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6550</v>
+        <v>6546</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>120.8488538240796</v>
+        <v>122.9643128989748</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>10.15</v>
+        <v>60.8</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>37.71016038069049</v>
+        <v>43.31637812868967</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.49129559995529</v>
+        <v>13.83901659727469</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.274882329744983</v>
+        <v>0.5149844874899007</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0473553316812067</v>
+        <v>-0.1271427532583298</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,52 +7099,105 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
+        <v>6550</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>北極星藥業-KY</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>120.8488538240796</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>37.71016038069049</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>18.49129559995529</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>1.274882329744983</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.0473553316812067</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>6552</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>易華電</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>105.2671523448428</v>
       </c>
-      <c r="E126" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>23.75</v>
       </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>34.98713342587249</v>
       </c>
-      <c r="I126" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>13.67888767386416</v>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.3485566889064521</v>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>-0.0306816845422283</v>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
